--- a/processos.xlsx
+++ b/processos.xlsx
@@ -5,42 +5,120 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId4"/>
+    <sheet name="tb_push_ia" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
-  <si>
-    <t>Descrição</t>
-  </si>
-  <si>
-    <t>Código do Processo</t>
-  </si>
-  <si>
-    <t>Processo ANVISA</t>
-  </si>
-  <si>
-    <t>0796/2026-39</t>
-  </si>
-  <si>
-    <t>Processo Exemplo 2</t>
-  </si>
-  <si>
-    <t>65508.001834/2026</t>
-  </si>
-  <si>
-    <t>processo3</t>
-  </si>
-  <si>
-    <t>80000.005920/2025-10</t>
-  </si>
-  <si>
-    <t>orignial</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="36">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>nup</t>
   </si>
   <si>
     <t>60080.000222/2025-78</t>
+  </si>
+  <si>
+    <t>64536.013335/2026-70</t>
+  </si>
+  <si>
+    <t>61165.000510/2026-36</t>
+  </si>
+  <si>
+    <t>60220.000111/2026-09</t>
+  </si>
+  <si>
+    <t>61001.006954/2024-96</t>
+  </si>
+  <si>
+    <t>00270.000127/2026-96</t>
+  </si>
+  <si>
+    <t>60090.000414/2024-84</t>
+  </si>
+  <si>
+    <t>64536.013525/2026-97</t>
+  </si>
+  <si>
+    <t>60588.000002/2026-14</t>
+  </si>
+  <si>
+    <t>63983.002916/2025-64</t>
+  </si>
+  <si>
+    <t>71000.088546/2024-16</t>
+  </si>
+  <si>
+    <t>60000.000575/2023-59</t>
+  </si>
+  <si>
+    <t>61001.000899/2026-92</t>
+  </si>
+  <si>
+    <t>60550.033464/2024-83</t>
+  </si>
+  <si>
+    <t>64536.013723/2026-51</t>
+  </si>
+  <si>
+    <t>60598.000054/2026-71</t>
+  </si>
+  <si>
+    <t>64536.013645/2026-94</t>
+  </si>
+  <si>
+    <t>64536.013907/2026-11</t>
+  </si>
+  <si>
+    <t>63011.001653/2026-44</t>
+  </si>
+  <si>
+    <t>19975.032817/2024-33</t>
+  </si>
+  <si>
+    <t>60041.000037/2026-21</t>
+  </si>
+  <si>
+    <t>60550.002162/2026-25</t>
+  </si>
+  <si>
+    <t>00058.095403/2025-20</t>
+  </si>
+  <si>
+    <t>60006.000021/2026-44</t>
+  </si>
+  <si>
+    <t>52315.100494/2023-86</t>
+  </si>
+  <si>
+    <t>60063.000014/2026-68</t>
+  </si>
+  <si>
+    <t>08001.003864/2023-80</t>
+  </si>
+  <si>
+    <t>64536.010006/2026-77</t>
+  </si>
+  <si>
+    <t>60000.002836/2026-18</t>
+  </si>
+  <si>
+    <t>00190.108129/2025-31</t>
+  </si>
+  <si>
+    <t>60080.000269/2021-16</t>
+  </si>
+  <si>
+    <t>02000.001930/2023-19</t>
+  </si>
+  <si>
+    <t>52315.100729/2023-30</t>
+  </si>
+  <si>
+    <t>02001.020690/2025-03</t>
   </si>
 </sst>
 </file>
@@ -52,9 +130,9 @@
   </numFmts>
   <fonts count="3">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Open Sans"/>
     </font>
     <font>
       <sz val="12"/>
@@ -114,7 +192,7 @@
     <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -141,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office Theme">
+    <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -181,7 +259,7 @@
         <a:srgbClr val="FF00FF"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office Theme">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
         <a:latin typeface="Helvetica Neue"/>
         <a:ea typeface="Helvetica Neue"/>
@@ -193,7 +271,7 @@
         <a:cs typeface="Helvetica Neue"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office Theme">
+    <a:fmtScheme name="Sheets">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -266,31 +344,13 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -351,23 +411,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="25400" cap="flat">
+        <a:ln w="12700" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:round/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
-            <a:srgbClr val="000000">
-              <a:alpha val="35000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
+        <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -395,10 +449,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="Open Sans"/>
+            <a:ea typeface="Open Sans"/>
+            <a:cs typeface="Open Sans"/>
+            <a:sym typeface="Open Sans"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -646,20 +700,14 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="25400" cap="flat">
+        <a:ln w="12700" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:round/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
-            <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
-            </a:srgbClr>
-          </a:outerShdw>
-        </a:effectLst>
+        <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
@@ -944,7 +992,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -972,10 +1020,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="Open Sans"/>
+            <a:ea typeface="Open Sans"/>
+            <a:cs typeface="Open Sans"/>
+            <a:sym typeface="Open Sans"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1226,106 +1274,321 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr defaultColWidth="14.4" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="8.85156" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.4219" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="14.4219" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1">
+    <row r="1" ht="12.75" customHeight="1">
       <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
       <c r="B1" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" t="s" s="2">
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="3">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="B2" t="s" s="2">
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="3">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" t="s" s="2">
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" s="3">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="B3" t="s" s="2">
+    </row>
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="3">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>5</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" t="s" s="2">
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="A6" s="3">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="2">
+    </row>
+    <row r="7" ht="12.75" customHeight="1">
+      <c r="A7" s="3">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" t="s" s="2">
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="3">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B5" t="s" s="2">
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="3">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" ht="13.55" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="3">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="3">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="3">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="3">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="A14" s="3">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="A15" s="3">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" ht="12.75" customHeight="1">
+      <c r="A16" s="3">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="12.75" customHeight="1">
+      <c r="A17" s="3">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" ht="12.75" customHeight="1">
+      <c r="A18" s="3">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" ht="12.75" customHeight="1">
+      <c r="A19" s="3">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" ht="12.75" customHeight="1">
+      <c r="A20" s="3">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="12.75" customHeight="1">
+      <c r="A21" s="3">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="12.75" customHeight="1">
+      <c r="A22" s="3">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="12.75" customHeight="1">
+      <c r="A23" s="3">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" ht="12.75" customHeight="1">
+      <c r="A24" s="3">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="12.75" customHeight="1">
+      <c r="A25" s="3">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" ht="12.75" customHeight="1">
+      <c r="A26" s="3">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" ht="12.75" customHeight="1">
+      <c r="A27" s="3">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" ht="12.75" customHeight="1">
+      <c r="A28" s="3">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" ht="12.75" customHeight="1">
+      <c r="A29" s="3">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" ht="12.75" customHeight="1">
+      <c r="A30" s="3">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" ht="12.75" customHeight="1">
+      <c r="A31" s="3">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" ht="12.75" customHeight="1">
+      <c r="A32" s="3">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" ht="12.75" customHeight="1">
+      <c r="A33" s="3">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" ht="12.75" customHeight="1">
+      <c r="A34" s="3">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" ht="12.75" customHeight="1">
+      <c r="A35" s="3">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" ht="12.75" customHeight="1">
+      <c r="A36" s="3">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="3">
+        <v>39</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" ht="12.75" customHeight="1">
+      <c r="A38" s="3">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
